--- a/public/assets/UL_specifika.xlsx
+++ b/public/assets/UL_specifika.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\talpas-invoice\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1255EF6C-E0BD-492C-844F-AAFD1AB7B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C404487-1942-4B1F-B390-76EA1A262795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{895A2A79-B7E7-4DE5-91AC-39E833A59D64}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Osnovno vzdrževanje in podpora AG</t>
   </si>
@@ -111,6 +111,15 @@
   </si>
   <si>
     <t>Osnovno vzdrževanje in podpora – Rektorat</t>
+  </si>
+  <si>
+    <t>UL VO</t>
+  </si>
+  <si>
+    <t>UL STAT</t>
+  </si>
+  <si>
+    <t>UL BM</t>
   </si>
 </sst>
 </file>
@@ -504,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24F956A3-D94B-42BB-81EE-A87F438EFF10}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="60.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
@@ -695,6 +704,24 @@
         <v>475</v>
       </c>
     </row>
+    <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
